--- a/tests/testdata/excel/空ブック.xlsx
+++ b/tests/testdata/excel/空ブック.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52ED673A-B1D9-423B-AE14-EC4368D1A56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B03DE16-CDF5-4C54-8DB3-E76CA0DD93C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{FD055664-B15C-42AE-8A07-6A5A9A59DEA5}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{A2CAF7E5-7BFE-42E1-9A94-0698B350798B}"/>
   </bookViews>
   <sheets>
     <sheet name="空" sheetId="1" r:id="rId1"/>
@@ -416,7 +416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6224BF01-5452-49AE-90C7-4B127B296C7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6DF21-1872-483E-AE04-9BA9EB99B586}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>

--- a/tests/testdata/excel/空ブック.xlsx
+++ b/tests/testdata/excel/空ブック.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B03DE16-CDF5-4C54-8DB3-E76CA0DD93C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BDA3039-9569-4776-8302-86A0A4879C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{A2CAF7E5-7BFE-42E1-9A94-0698B350798B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{52C11F8E-BFA3-41CA-9F29-3672F075E8AD}"/>
   </bookViews>
   <sheets>
     <sheet name="空" sheetId="1" r:id="rId1"/>
@@ -416,7 +416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AD6DF21-1872-483E-AE04-9BA9EB99B586}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1E2CCF-0971-465D-B4DD-F8546E77E33F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData/>
